--- a/data/trans_orig/P1415-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2012</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445876</t>
+          <t>446068</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453279</t>
+          <t>453278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423541</t>
+          <t>424404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>874597</t>
+          <t>873777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>882535</t>
+          <t>882452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680285</t>
+          <t>680459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>598075</t>
+          <t>598886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609250</t>
+          <t>609253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1284006</t>
+          <t>1284243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1295330</t>
+          <t>1294804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>26832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666972</t>
+          <t>666775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679004</t>
+          <t>679008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>692638</t>
+          <t>691811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704810</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1363996</t>
+          <t>1364605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1381522</t>
+          <t>1381673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20715</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593902</t>
+          <t>593162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610234</t>
+          <t>610286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597624</t>
+          <t>597238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611140</t>
+          <t>611035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1197779</t>
+          <t>1198417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1218373</t>
+          <t>1218245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>25327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410983</t>
+          <t>412403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>425251</t>
+          <t>426149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>434640</t>
+          <t>435431</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445694</t>
+          <t>445752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>853033</t>
+          <t>851902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869015</t>
+          <t>868893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22527</t>
+          <t>22893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>26611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287259</t>
+          <t>286893</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302995</t>
+          <t>302041</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>347245</t>
+          <t>348069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>639718</t>
+          <t>637171</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>655826</t>
+          <t>654972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>227983</t>
+          <t>228305</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242476</t>
+          <t>242451</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>377650</t>
+          <t>378734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387820</t>
+          <t>387812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>610461</t>
+          <t>611192</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628597</t>
+          <t>628383</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42583</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75958</t>
+          <t>76481</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26002</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52895</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77082</t>
+          <t>72883</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116625</t>
+          <t>114447</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3350821</t>
+          <t>3350298</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3384196</t>
+          <t>3384042</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3502203</t>
+          <t>3504508</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3529096</t>
+          <t>3529767</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6865252</t>
+          <t>6867430</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6904795</t>
+          <t>6908994</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2016</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413725</t>
+          <t>414065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386239</t>
+          <t>386828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394802</t>
+          <t>394797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>804033</t>
+          <t>805554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813354</t>
+          <t>813352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>19004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>582082</t>
+          <t>582386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589599</t>
+          <t>589595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>548314</t>
+          <t>548777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>559043</t>
+          <t>559799</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1134415</t>
+          <t>1135036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1148061</t>
+          <t>1147660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12526</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658265</t>
+          <t>658290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667276</t>
+          <t>667263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648860</t>
+          <t>648803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658551</t>
+          <t>658560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1309932</t>
+          <t>1310755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1323971</t>
+          <t>1324084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>633483</t>
+          <t>632572</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643962</t>
+          <t>643858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630383</t>
+          <t>630541</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643652</t>
+          <t>643712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1267661</t>
+          <t>1269155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1285530</t>
+          <t>1285539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>27793</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>464359</t>
+          <t>464556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474865</t>
+          <t>475746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>477964</t>
+          <t>477965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>491807</t>
+          <t>491407</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>946731</t>
+          <t>946974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>965003</t>
+          <t>964627</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322004</t>
+          <t>320912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332762</t>
+          <t>332761</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>364225</t>
+          <t>364022</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>374701</t>
+          <t>374722</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>690923</t>
+          <t>690061</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>705843</t>
+          <t>705406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20047</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29508</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242118</t>
+          <t>241409</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252783</t>
+          <t>253119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380122</t>
+          <t>380834</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395640</t>
+          <t>396355</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>627659</t>
+          <t>628662</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>646692</t>
+          <t>647339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48157</t>
+          <t>48341</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42821</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72320</t>
+          <t>74023</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74075</t>
+          <t>74417</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114000</t>
+          <t>112707</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3346193</t>
+          <t>3346009</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3369196</t>
+          <t>3369276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3472222</t>
+          <t>3470519</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3501721</t>
+          <t>3503149</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6824892</t>
+          <t>6826185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6864817</t>
+          <t>6864475</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P1415-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446068</t>
+          <t>446441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453278</t>
+          <t>453275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424404</t>
+          <t>423889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>873777</t>
+          <t>873802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>882452</t>
+          <t>882579</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680459</t>
+          <t>680053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>598886</t>
+          <t>599077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609253</t>
+          <t>609247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1284243</t>
+          <t>1283800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294804</t>
+          <t>1294793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>17893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>27747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666775</t>
+          <t>666720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679008</t>
+          <t>678957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>691811</t>
+          <t>691681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>704590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1364605</t>
+          <t>1363690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1381673</t>
+          <t>1381624</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30463</t>
+          <t>31249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593162</t>
+          <t>594538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610286</t>
+          <t>609894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597238</t>
+          <t>598587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611035</t>
+          <t>611016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1198417</t>
+          <t>1197631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1218245</t>
+          <t>1218376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>24590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>412403</t>
+          <t>410100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>426149</t>
+          <t>425257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>435431</t>
+          <t>435504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445752</t>
+          <t>445758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>851902</t>
+          <t>852639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>868893</t>
+          <t>868942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22893</t>
+          <t>22393</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26611</t>
+          <t>26398</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286893</t>
+          <t>287393</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302041</t>
+          <t>302757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>347159</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>637171</t>
+          <t>637384</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>654972</t>
+          <t>655011</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>22008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27638</t>
+          <t>27309</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228305</t>
+          <t>227843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242451</t>
+          <t>242864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>378734</t>
+          <t>378084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387812</t>
+          <t>387895</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>611192</t>
+          <t>611521</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628383</t>
+          <t>628885</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42737</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>76481</t>
+          <t>75389</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>53439</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72883</t>
+          <t>75669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114447</t>
+          <t>116553</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3350298</t>
+          <t>3351390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3384042</t>
+          <t>3384422</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3504508</t>
+          <t>3501659</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3529767</t>
+          <t>3527906</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6867430</t>
+          <t>6865324</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6908994</t>
+          <t>6906208</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3730,77 +3730,77 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3822</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9506</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10516</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3822</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8927</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4719</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9664</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414065</t>
+          <t>414315</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3838,77 +3838,77 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>391933</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>386249</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>394798</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>810499</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>804702</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>813351</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>98,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>391933</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>386828</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>394797</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>810499</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>805554</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>813352</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>20125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>582386</t>
+          <t>582399</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589595</t>
+          <t>589604</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>548777</t>
+          <t>547824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>559799</t>
+          <t>558958</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1135036</t>
+          <t>1133915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1147660</t>
+          <t>1148218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658290</t>
+          <t>658112</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667263</t>
+          <t>667273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648803</t>
+          <t>648627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658560</t>
+          <t>658542</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1310755</t>
+          <t>1309900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324084</t>
+          <t>1323211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632572</t>
+          <t>632520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643858</t>
+          <t>643091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630541</t>
+          <t>629679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643712</t>
+          <t>643798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1269155</t>
+          <t>1268086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1285539</t>
+          <t>1284945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27793</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>464556</t>
+          <t>463315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475746</t>
+          <t>474886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>477965</t>
+          <t>478647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>491407</t>
+          <t>492207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>946974</t>
+          <t>947687</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>964627</t>
+          <t>965044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>20706</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320912</t>
+          <t>321891</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332761</t>
+          <t>332763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>364022</t>
+          <t>363193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>374722</t>
+          <t>374706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>690061</t>
+          <t>691386</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>705406</t>
+          <t>705988</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19335</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>241409</t>
+          <t>242341</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253119</t>
+          <t>253177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380834</t>
+          <t>380125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396355</t>
+          <t>395671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>628662</t>
+          <t>628637</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>647339</t>
+          <t>646676</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48341</t>
+          <t>49154</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41393</t>
+          <t>43365</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74023</t>
+          <t>72730</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74417</t>
+          <t>74796</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112707</t>
+          <t>112608</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3346009</t>
+          <t>3345196</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3369276</t>
+          <t>3370188</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3470519</t>
+          <t>3471812</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3503149</t>
+          <t>3501177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6826185</t>
+          <t>6826284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6864475</t>
+          <t>6864096</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
